--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.76917687977516</v>
+      </c>
+      <c r="C2">
         <v>32.18303648696541</v>
-      </c>
-      <c r="C2">
-        <v>25.76917687977516</v>
       </c>
       <c r="D2">
         <v>3.107227002663389</v>
       </c>
       <c r="E2">
-        <v>20.37517284562603</v>
+        <v>16.31453990451094</v>
       </c>
       <c r="F2">
         <v>63.31028724986302</v>
       </c>
       <c r="G2">
-        <v>16.31453990451094</v>
+        <v>20.37517284562603</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.96686072548141</v>
+      </c>
+      <c r="C3">
         <v>39.43125839677564</v>
-      </c>
-      <c r="C3">
-        <v>27.96686072548141</v>
       </c>
       <c r="D3">
         <v>2.536059057353776</v>
       </c>
       <c r="E3">
-        <v>23.5553772070626</v>
+        <v>16.7067950775816</v>
       </c>
       <c r="F3">
         <v>59.73782771535581</v>
       </c>
       <c r="G3">
-        <v>16.7067950775816</v>
+        <v>23.5553772070626</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.76489423127395</v>
+      </c>
+      <c r="C4">
         <v>26.36082095428062</v>
-      </c>
-      <c r="C4">
-        <v>28.76489423127395</v>
       </c>
       <c r="D4">
         <v>3.793508562325766</v>
       </c>
       <c r="E4">
-        <v>16.99319866003452</v>
+        <v>18.54295672182181</v>
       </c>
       <c r="F4">
-        <v>64.46384461814368</v>
+        <v>64.46384461814367</v>
       </c>
       <c r="G4">
-        <v>18.54295672182181</v>
+        <v>16.99319866003451</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.22582352162985</v>
+      </c>
+      <c r="C5">
         <v>38.788199497288</v>
-      </c>
-      <c r="C5">
-        <v>27.22582352162985</v>
       </c>
       <c r="D5">
         <v>2.578103683492496</v>
       </c>
       <c r="E5">
-        <v>23.36441150689298</v>
+        <v>16.39971312455176</v>
       </c>
       <c r="F5">
         <v>60.23587536855526</v>
       </c>
       <c r="G5">
-        <v>16.39971312455176</v>
+        <v>23.36441150689298</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.62453684643886</v>
+      </c>
+      <c r="C6">
         <v>38.78139151914368</v>
-      </c>
-      <c r="C6">
-        <v>27.62453684643886</v>
       </c>
       <c r="D6">
         <v>2.578556263269639</v>
       </c>
       <c r="E6">
-        <v>23.30529440870856</v>
+        <v>16.60069272637308</v>
       </c>
       <c r="F6">
         <v>60.09401286491835</v>
       </c>
       <c r="G6">
-        <v>16.60069272637308</v>
+        <v>23.30529440870856</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>24.90087232355274</v>
+      </c>
+      <c r="C7">
         <v>39.32064499074809</v>
-      </c>
-      <c r="C7">
-        <v>24.90087232355274</v>
       </c>
       <c r="D7">
         <v>2.543193277310924</v>
       </c>
       <c r="E7">
-        <v>23.94366197183099</v>
+        <v>15.16297786720322</v>
       </c>
       <c r="F7">
         <v>60.89336016096579</v>
       </c>
       <c r="G7">
-        <v>15.16297786720322</v>
+        <v>23.94366197183099</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.81740383749212</v>
+      </c>
+      <c r="C8">
         <v>45.46437257904693</v>
-      </c>
-      <c r="C8">
-        <v>26.81740383749212</v>
       </c>
       <c r="D8">
         <v>2.199524469982168</v>
       </c>
       <c r="E8">
-        <v>26.38954248366013</v>
+        <v>15.56601307189542</v>
       </c>
       <c r="F8">
         <v>58.04444444444444</v>
       </c>
       <c r="G8">
-        <v>15.56601307189542</v>
+        <v>26.38954248366013</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>26.39787798408488</v>
+      </c>
+      <c r="C9">
         <v>41.15649867374005</v>
-      </c>
-      <c r="C9">
-        <v>26.39787798408488</v>
       </c>
       <c r="D9">
         <v>2.4297499355504</v>
       </c>
       <c r="E9">
-        <v>24.56306990881459</v>
+        <v>15.7548125633232</v>
       </c>
       <c r="F9">
         <v>59.6821175278622</v>
       </c>
       <c r="G9">
-        <v>15.7548125633232</v>
+        <v>24.56306990881459</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.25925237121071</v>
+      </c>
+      <c r="C10">
         <v>39.0087409336061</v>
-      </c>
-      <c r="C10">
-        <v>28.25925237121071</v>
       </c>
       <c r="D10">
         <v>2.563528009535161</v>
       </c>
       <c r="E10">
-        <v>23.32110295752724</v>
+        <v>16.8945963975984</v>
       </c>
       <c r="F10">
         <v>59.78430064487436</v>
       </c>
       <c r="G10">
-        <v>16.8945963975984</v>
+        <v>23.32110295752724</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.88389349628983</v>
+      </c>
+      <c r="C11">
         <v>43.53266404772297</v>
-      </c>
-      <c r="C11">
-        <v>25.88389349628983</v>
       </c>
       <c r="D11">
         <v>2.297125668449198</v>
       </c>
       <c r="E11">
-        <v>25.69563723806252</v>
+        <v>15.27825489522501</v>
       </c>
       <c r="F11">
         <v>59.02610786671247</v>
       </c>
       <c r="G11">
-        <v>15.27825489522501</v>
+        <v>25.69563723806252</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>24.10651716888577</v>
+      </c>
+      <c r="C12">
         <v>53.92431674842327</v>
-      </c>
-      <c r="C12">
-        <v>24.10651716888577</v>
       </c>
       <c r="D12">
         <v>1.85445094217024</v>
       </c>
       <c r="E12">
-        <v>30.28931312733713</v>
+        <v>13.54064160598307</v>
       </c>
       <c r="F12">
         <v>56.17004526667979</v>
       </c>
       <c r="G12">
-        <v>13.54064160598307</v>
+        <v>30.28931312733713</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.68756530825496</v>
+      </c>
+      <c r="C13">
         <v>43.15569487983282</v>
-      </c>
-      <c r="C13">
-        <v>26.68756530825496</v>
       </c>
       <c r="D13">
         <v>2.317191283292978</v>
       </c>
       <c r="E13">
-        <v>25.40913006029285</v>
+        <v>15.71305524793897</v>
       </c>
       <c r="F13">
         <v>58.87781469176818</v>
       </c>
       <c r="G13">
-        <v>15.71305524793897</v>
+        <v>25.40913006029285</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.768</v>
+      </c>
+      <c r="C14">
         <v>49.568</v>
-      </c>
-      <c r="C14">
-        <v>24.768</v>
       </c>
       <c r="D14">
         <v>2.017430600387347</v>
       </c>
       <c r="E14">
-        <v>28.43245227606462</v>
+        <v>14.20704845814978</v>
       </c>
       <c r="F14">
         <v>57.36049926578561</v>
       </c>
       <c r="G14">
-        <v>14.20704845814978</v>
+        <v>28.43245227606461</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.90152565880721</v>
+      </c>
+      <c r="C15">
         <v>50.55478502080444</v>
-      </c>
-      <c r="C15">
-        <v>25.90152565880721</v>
       </c>
       <c r="D15">
         <v>1.978052126200274</v>
       </c>
       <c r="E15">
-        <v>28.65002947533897</v>
+        <v>14.67871880526626</v>
       </c>
       <c r="F15">
         <v>56.67125171939477</v>
       </c>
       <c r="G15">
-        <v>14.67871880526626</v>
+        <v>28.65002947533897</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>32.10470085470086</v>
+      </c>
+      <c r="C16">
         <v>34.82905982905983</v>
-      </c>
-      <c r="C16">
-        <v>32.10470085470086</v>
       </c>
       <c r="D16">
         <v>2.871165644171779</v>
       </c>
       <c r="E16">
-        <v>20.864</v>
+        <v>19.232</v>
       </c>
       <c r="F16">
         <v>59.904</v>
       </c>
       <c r="G16">
-        <v>19.232</v>
+        <v>20.864</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.27461139896373</v>
+      </c>
+      <c r="C17">
         <v>47.81643227239083</v>
-      </c>
-      <c r="C17">
-        <v>29.27461139896373</v>
       </c>
       <c r="D17">
         <v>2.091331269349845</v>
       </c>
       <c r="E17">
-        <v>27.00104493207942</v>
+        <v>16.53082549634274</v>
       </c>
       <c r="F17">
         <v>56.46812957157785</v>
       </c>
       <c r="G17">
-        <v>16.53082549634274</v>
+        <v>27.00104493207942</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.05313150197509</v>
+      </c>
+      <c r="C18">
         <v>38.34092211199228</v>
-      </c>
-      <c r="C18">
-        <v>26.05313150197509</v>
       </c>
       <c r="D18">
         <v>2.608179315768777</v>
       </c>
       <c r="E18">
-        <v>23.32257236142192</v>
+        <v>15.84797681499688</v>
       </c>
       <c r="F18">
         <v>60.8294508235812</v>
       </c>
       <c r="G18">
-        <v>15.84797681499688</v>
+        <v>23.32257236142192</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.948217769108</v>
+      </c>
+      <c r="C19">
         <v>31.88508600815748</v>
-      </c>
-      <c r="C19">
-        <v>27.948217769108</v>
       </c>
       <c r="D19">
         <v>3.136262513904338</v>
       </c>
       <c r="E19">
-        <v>19.94896260956396</v>
+        <v>17.48585376678131</v>
       </c>
       <c r="F19">
         <v>62.56518362365472</v>
       </c>
       <c r="G19">
-        <v>17.48585376678131</v>
+        <v>19.94896260956396</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>30.67331670822943</v>
+      </c>
+      <c r="C20">
         <v>23.5482721767011</v>
-      </c>
-      <c r="C20">
-        <v>30.67331670822943</v>
       </c>
       <c r="D20">
         <v>4.246596066565809</v>
       </c>
       <c r="E20">
+        <v>19.88911988911989</v>
+      </c>
+      <c r="F20">
+        <v>64.84176484176483</v>
+      </c>
+      <c r="G20">
         <v>15.26911526911527</v>
-      </c>
-      <c r="F20">
-        <v>64.84176484176484</v>
-      </c>
-      <c r="G20">
-        <v>19.88911988911989</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>31.30434782608696</v>
+      </c>
+      <c r="C21">
         <v>43.47826086956522</v>
-      </c>
-      <c r="C21">
-        <v>31.30434782608696</v>
       </c>
       <c r="D21">
         <v>2.3</v>
       </c>
       <c r="E21">
-        <v>24.87562189054727</v>
+        <v>17.91044776119403</v>
       </c>
       <c r="F21">
         <v>57.2139303482587</v>
       </c>
       <c r="G21">
-        <v>17.91044776119403</v>
+        <v>24.87562189054727</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.11489040060469</v>
+      </c>
+      <c r="C22">
         <v>38.1204333585286</v>
-      </c>
-      <c r="C22">
-        <v>26.11489040060469</v>
       </c>
       <c r="D22">
         <v>2.623265036351619</v>
       </c>
       <c r="E22">
-        <v>23.2108613944926</v>
+        <v>15.90089744573138</v>
       </c>
       <c r="F22">
         <v>60.88824115977602</v>
       </c>
       <c r="G22">
-        <v>15.90089744573138</v>
+        <v>23.2108613944926</v>
       </c>
     </row>
   </sheetData>
